--- a/_business/质检表格.xlsx
+++ b/_business/质检表格.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="13680" activeTab="1"/>
+    <workbookView windowWidth="21000" windowHeight="14280"/>
   </bookViews>
   <sheets>
     <sheet name="采购单明细导出" sheetId="2" r:id="rId1"/>
@@ -131,7 +131,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="28">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -161,7 +161,23 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -317,7 +333,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -333,12 +349,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEBF1F8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF003366"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -647,31 +657,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -680,119 +678,131 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -817,13 +827,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1160,72 +1188,76 @@
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="2" ht="29" customHeight="1" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="12">
         <v>3220</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="13">
         <v>11</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="15">
         <v>3220</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="16">
         <v>11</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:5">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="12">
         <v>3220</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="13">
         <v>11</v>
       </c>
     </row>
